--- a/artfynd/A 44954-2022 artfynd.xlsx
+++ b/artfynd/A 44954-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123949132</v>
+        <v>123949142</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>95683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123949142</v>
+        <v>123949132</v>
       </c>
       <c r="B3" t="n">
-        <v>95175</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +812,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 44954-2022 artfynd.xlsx
+++ b/artfynd/A 44954-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123949142</v>
+        <v>123949132</v>
       </c>
       <c r="B2" t="n">
-        <v>95683</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123949132</v>
+        <v>123949142</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>95683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,27 +808,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 44954-2022 artfynd.xlsx
+++ b/artfynd/A 44954-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123949142</v>
+        <v>123949132</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123949132</v>
+        <v>123949142</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,27 +808,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 44954-2022 artfynd.xlsx
+++ b/artfynd/A 44954-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123949132</v>
+        <v>123949142</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>95705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123949142</v>
+        <v>123949132</v>
       </c>
       <c r="B3" t="n">
-        <v>95705</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +812,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
